--- a/Team-Data/2014-15/3-17-2014-15.xlsx
+++ b/Team-Data/2014-15/3-17-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>6.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -775,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
@@ -981,10 +1048,10 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -1118,16 +1185,16 @@
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" t="n">
         <v>29</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>0.439</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,7 +1292,7 @@
         <v>35.8</v>
       </c>
       <c r="J5" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.424</v>
@@ -1237,16 +1304,16 @@
         <v>18.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="O5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R5" t="n">
         <v>10</v>
@@ -1261,7 +1328,7 @@
         <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="W5" t="n">
         <v>5.9</v>
@@ -1273,31 +1340,31 @@
         <v>5.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI5" t="n">
         <v>26</v>
@@ -1324,7 +1391,7 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1345,16 +1412,16 @@
         <v>30</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1527,10 +1594,10 @@
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
         <v>2</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
         <v>24</v>
@@ -1667,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK7" t="n">
         <v>10</v>
@@ -1688,22 +1755,22 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
         <v>19</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1712,7 +1779,7 @@
         <v>25</v>
       </c>
       <c r="AY7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1724,7 +1791,7 @@
         <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
         <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.642</v>
+        <v>0.632</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,10 +1838,10 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L8" t="n">
         <v>9.300000000000001</v>
@@ -1783,7 +1850,7 @@
         <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
@@ -1792,19 +1859,19 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>10.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
         <v>12.7</v>
@@ -1825,25 +1892,25 @@
         <v>21.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.9</v>
+        <v>104.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1867,16 +1934,16 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>23</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
@@ -2049,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.358</v>
+        <v>0.348</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,22 +2202,22 @@
         <v>36.7</v>
       </c>
       <c r="J10" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.427</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O10" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P10" t="n">
         <v>22.8</v>
@@ -2159,19 +2226,19 @@
         <v>0.707</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S10" t="n">
         <v>32.2</v>
       </c>
       <c r="T10" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>7.7</v>
@@ -2183,19 +2250,19 @@
         <v>5</v>
       </c>
       <c r="Z10" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>98</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,25 +2274,25 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
         <v>28</v>
       </c>
       <c r="AL10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM10" t="n">
         <v>11</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
@@ -2261,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
         <v>23</v>
@@ -2434,7 +2501,7 @@
         <v>19</v>
       </c>
       <c r="AW11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2496,13 +2563,13 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
@@ -2514,13 +2581,13 @@
         <v>0.343</v>
       </c>
       <c r="O12" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
         <v>12</v>
@@ -2532,7 +2599,7 @@
         <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="V12" t="n">
         <v>16.7</v>
@@ -2541,25 +2608,25 @@
         <v>9.6</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
         <v>103</v>
       </c>
       <c r="AC12" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2571,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ12" t="n">
         <v>11</v>
@@ -2595,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>27</v>
@@ -2604,22 +2671,22 @@
         <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW12" t="n">
         <v>2</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2628,7 +2695,7 @@
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>0.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>17</v>
@@ -2753,13 +2820,13 @@
         <v>17</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK13" t="n">
         <v>23</v>
@@ -2780,7 +2847,7 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -2801,7 +2868,7 @@
         <v>28</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY13" t="n">
         <v>17</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.632</v>
+        <v>0.627</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2890,7 +2957,7 @@
         <v>9.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T14" t="n">
         <v>42.3</v>
@@ -2902,7 +2969,7 @@
         <v>12.3</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X14" t="n">
         <v>4.9</v>
@@ -2911,37 +2978,37 @@
         <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA14" t="n">
         <v>21.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC14" t="n">
         <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK14" t="n">
         <v>2</v>
@@ -2980,7 +3047,7 @@
         <v>2</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>9</v>
@@ -2989,10 +3056,10 @@
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
         <v>17</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>0.262</v>
+        <v>0.258</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
-        <v>86.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U15" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V15" t="n">
         <v>13.2</v>
@@ -3093,19 +3160,19 @@
         <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3123,13 +3190,13 @@
         <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM15" t="n">
         <v>24</v>
@@ -3144,10 +3211,10 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
         <v>13</v>
@@ -3165,16 +3232,16 @@
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY15" t="n">
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA15" t="n">
         <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>23</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
         <v>47</v>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3230,16 +3297,16 @@
         <v>82.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>15.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.337</v>
+        <v>0.333</v>
       </c>
       <c r="O16" t="n">
         <v>18.2</v>
@@ -3248,7 +3315,7 @@
         <v>23.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
         <v>10.5</v>
@@ -3260,7 +3327,7 @@
         <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V16" t="n">
         <v>13.4</v>
@@ -3275,19 +3342,19 @@
         <v>5.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3317,7 +3384,7 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO16" t="n">
         <v>7</v>
@@ -3329,7 +3396,7 @@
         <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS16" t="n">
         <v>14</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3350,10 +3417,10 @@
         <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA16" t="n">
         <v>14</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3493,7 +3560,7 @@
         <v>11</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>19</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J18" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.367</v>
+        <v>0.37</v>
       </c>
       <c r="O18" t="n">
         <v>16.1</v>
@@ -3618,22 +3685,22 @@
         <v>10.1</v>
       </c>
       <c r="S18" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V18" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="W18" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y18" t="n">
         <v>4.7</v>
@@ -3645,13 +3712,13 @@
         <v>20</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3660,10 +3727,10 @@
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
         <v>18</v>
@@ -3684,13 +3751,13 @@
         <v>4</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP18" t="n">
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3705,16 +3772,16 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
       </c>
       <c r="AY18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
         <v>25</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3872,7 +3939,7 @@
         <v>2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
         <v>3</v>
@@ -3884,10 +3951,10 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>9</v>
@@ -3902,7 +3969,7 @@
         <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -3952,52 +4019,52 @@
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O20" t="n">
         <v>16.8</v>
       </c>
       <c r="P20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="R20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="S20" t="n">
+        <v>32</v>
+      </c>
+      <c r="T20" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="U20" t="n">
         <v>21.9</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.769</v>
-      </c>
-      <c r="R20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>22</v>
-      </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.8</v>
@@ -4006,16 +4073,16 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
@@ -4045,28 +4112,28 @@
         <v>23</v>
       </c>
       <c r="AN20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR20" t="n">
         <v>8</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -4119,70 +4186,70 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>0.209</v>
+        <v>0.197</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
         <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.348</v>
+        <v>0.349</v>
       </c>
       <c r="O21" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="P21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R21" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T21" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U21" t="n">
         <v>21.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -4191,16 +4258,16 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>92.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.9</v>
+        <v>-9.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF21" t="n">
         <v>30</v>
@@ -4209,25 +4276,25 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
         <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AM21" t="n">
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4257,7 +4324,7 @@
         <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4418,7 +4485,7 @@
         <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4433,7 +4500,7 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -4498,55 +4565,55 @@
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J23" t="n">
         <v>82.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="O23" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P23" t="n">
         <v>19.6</v>
       </c>
-      <c r="N23" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="O23" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="P23" t="n">
-        <v>19.5</v>
-      </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
         <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.8</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.3</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W23" t="n">
         <v>7.8</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
         <v>21</v>
@@ -4555,10 +4622,10 @@
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-5.9</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
@@ -4579,13 +4646,13 @@
         <v>16</v>
       </c>
       <c r="AJ23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
         <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4606,7 +4673,7 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
@@ -4615,16 +4682,16 @@
         <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>18</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>16</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -4931,10 +4998,10 @@
         <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>4</v>
@@ -4961,7 +5028,7 @@
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ25" t="n">
         <v>9</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5180,7 @@
         <v>4</v>
       </c>
       <c r="AF26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG26" t="n">
         <v>4</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -5396,13 +5463,13 @@
         <v>65</v>
       </c>
       <c r="E28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.615</v>
+        <v>0.631</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,52 +5478,52 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>84</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.367</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P28" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.773</v>
+        <v>0.772</v>
       </c>
       <c r="R28" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U28" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="W28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z28" t="n">
         <v>19.5</v>
@@ -5468,7 +5535,7 @@
         <v>102.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="n">
         <v>27</v>
@@ -5477,10 +5544,10 @@
         <v>9</v>
       </c>
       <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>7</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>9</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
@@ -5495,22 +5562,22 @@
         <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
@@ -5519,19 +5586,19 @@
         <v>7</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>11</v>
@@ -5546,7 +5613,7 @@
         <v>11</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5713,7 +5780,7 @@
         <v>15</v>
       </c>
       <c r="AX29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY29" t="n">
         <v>19</v>
@@ -5722,7 +5789,7 @@
         <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
@@ -5865,7 +5932,7 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
         <v>18</v>
@@ -5895,7 +5962,7 @@
         <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6035,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK31" t="n">
         <v>3</v>
@@ -6047,7 +6114,7 @@
         <v>27</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6068,16 +6135,16 @@
         <v>12</v>
       </c>
       <c r="AU31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
       </c>
       <c r="AX31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-17-2014-15</t>
+          <t>2015-03-17</t>
         </is>
       </c>
     </row>
